--- a/data/evaluation/risk_assessment_checklist.xlsx
+++ b/data/evaluation/risk_assessment_checklist.xlsx
@@ -1504,25 +1504,29 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr"/>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Trade Risk</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Political Risk; Trade Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3">
@@ -1548,25 +1552,29 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Trade Risk</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Political Risk; Trade Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -1592,29 +1600,25 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -1640,29 +1644,25 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
@@ -1688,25 +1688,25 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr"/>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
@@ -1732,25 +1732,25 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -1776,21 +1776,25 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
@@ -1816,21 +1820,25 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -1856,25 +1864,25 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Trade Risk</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
@@ -1900,25 +1908,25 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Trade Risk</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
@@ -1944,29 +1952,25 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
@@ -1992,29 +1996,25 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="14">
@@ -2040,25 +2040,29 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="15">
@@ -2084,25 +2088,29 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16">
@@ -2128,25 +2136,29 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Political Risk</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17">
@@ -2172,25 +2184,29 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Political Risk</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
@@ -2216,22 +2232,26 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="I18" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>0.5</v>
@@ -2260,22 +2280,26 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.5</v>
@@ -2304,22 +2328,26 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>0.5</v>
@@ -2348,22 +2376,26 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.5</v>
@@ -2392,29 +2424,25 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="23">
@@ -2440,29 +2468,25 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="24">
@@ -2488,7 +2512,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2510,7 +2534,7 @@
         <v>0.5</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="25">
@@ -2536,7 +2560,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2558,7 +2582,7 @@
         <v>0.5</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="26">
@@ -2584,25 +2608,29 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="I26" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27">
@@ -2628,25 +2656,29 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="I27" s="2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="28">
@@ -2672,25 +2704,25 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Trade Risk</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="I28" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="29">
@@ -2716,25 +2748,25 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Trade Risk</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="I29" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="30">
@@ -2760,25 +2792,29 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Political Risk</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Trade Risk</t>
+        </is>
+      </c>
       <c r="I30" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
@@ -2804,25 +2840,29 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Political Risk</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Trade Risk</t>
+        </is>
+      </c>
       <c r="I31" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32">
@@ -2848,25 +2888,29 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Political Risk</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Trade Risk</t>
+        </is>
+      </c>
       <c r="I32" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
@@ -2892,25 +2936,29 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Political Risk</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Trade Risk</t>
+        </is>
+      </c>
       <c r="I33" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
@@ -2936,26 +2984,26 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Market Access Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>0.5</v>
@@ -2984,26 +3032,26 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Trade Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Market Access Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.5</v>
@@ -3080,19 +3128,19 @@
         <v>14</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.143</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.143</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3167,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -3180,19 +3228,19 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.167</v>
-      </c>
       <c r="G6" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
@@ -3217,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3327,7 +3375,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3342,7 +3390,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -3352,7 +3400,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -3382,7 +3430,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -3397,7 +3445,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
@@ -3407,7 +3455,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
@@ -3437,7 +3485,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -3452,7 +3500,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3462,7 +3510,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K4" s="2" t="n">
@@ -3507,7 +3555,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3547,7 +3595,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -3562,7 +3610,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3602,7 +3650,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3617,7 +3665,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3627,7 +3675,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K7" s="2" t="n">
@@ -3657,7 +3705,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3672,7 +3720,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3682,7 +3730,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K8" s="2" t="n">
@@ -3712,7 +3760,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -3727,7 +3775,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -3737,7 +3785,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K9" s="2" t="n">
@@ -3767,7 +3815,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -3792,7 +3840,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K10" s="2" t="n">
@@ -3822,7 +3870,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3837,7 +3885,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3847,7 +3895,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K11" s="2" t="n">
@@ -3877,7 +3925,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3892,7 +3940,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -3902,7 +3950,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K12" s="2" t="n">
@@ -3947,17 +3995,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -3987,7 +4035,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4002,7 +4050,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4012,7 +4060,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -4057,7 +4105,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -4097,7 +4145,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4112,7 +4160,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4122,7 +4170,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -4167,7 +4215,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4207,7 +4255,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4232,7 +4280,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K18" s="2" t="n">
@@ -4288,10 +4336,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.461</v>
+        <v>0.779</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.461</v>
+        <v>0.779</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -4306,10 +4354,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.676</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.676</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -4324,10 +4372,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -4342,10 +4390,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -4367,7 +4415,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>L1：语料层面。六类风险在 47 篇语料中均有标注，缺失的是「与案例挂钩」的证据</t>
+          <t>L1：语料层面。六类风险在 30 篇语料中均有标注（不含 held-out 案例），缺失的是「与案例挂钩」的证据</t>
         </is>
       </c>
     </row>
@@ -4378,10 +4426,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.711</v>
+        <v>0.966</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.711</v>
+        <v>0.966</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -4396,10 +4444,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.461</v>
+        <v>0.779</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.461</v>
+        <v>0.779</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -4423,7 +4471,7 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk=14; Political Risk=5; Supply Chain Risk=28; Regulatory Risk=10; Market Access Risk=14; Operational Risk=24</t>
+          <t>Trade Risk=14; Political Risk=5; Supply Chain Risk=11; Regulatory Risk=10; Market Access Risk=14; Operational Risk=7</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/risk_assessment_checklist.xlsx
+++ b/data/evaluation/risk_assessment_checklist.xlsx
@@ -1552,7 +1552,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1567,14 +1567,14 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Supply Chain Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -1644,25 +1644,29 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Supply Chain Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="6">
@@ -1732,25 +1736,25 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Regulatory Risk</t>
-        </is>
-      </c>
+          <t>Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="8">
@@ -1776,7 +1780,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1787,14 +1791,14 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -1820,7 +1824,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1829,16 +1833,12 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Regulatory Risk</t>
-        </is>
-      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1917,16 +1917,12 @@
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Regulatory Risk</t>
-        </is>
-      </c>
+      <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1996,25 +1992,29 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
+          <t>Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Supply Chain Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="14">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2101,16 +2101,12 @@
           <t>Political Risk</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Regulatory Risk</t>
-        </is>
-      </c>
+      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="16">
@@ -2184,7 +2180,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2199,14 +2195,14 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="18">
@@ -2512,7 +2508,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2534,7 +2530,7 @@
         <v>0.5</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
@@ -2560,7 +2556,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2582,7 +2578,7 @@
         <v>0.5</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
@@ -2792,26 +2788,22 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Trade Risk</t>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.5</v>
@@ -2888,26 +2880,22 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Trade Risk</t>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.5</v>
@@ -3153,13 +3141,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -3215,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -3231,13 +3219,13 @@
         <v>6</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>11</v>
@@ -3265,7 +3253,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3375,7 +3363,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3400,7 +3388,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -3430,7 +3418,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -3595,7 +3583,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -3650,7 +3638,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -3830,7 +3818,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4000,7 +3988,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4035,7 +4023,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4060,7 +4048,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -4270,7 +4258,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -4336,10 +4324,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.779</v>
+        <v>0.819</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.779</v>
+        <v>0.721</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -4354,10 +4342,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.652</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -4372,10 +4360,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -4390,10 +4378,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -4415,7 +4403,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>L1：语料层面。六类风险在 30 篇语料中均有标注（不含 held-out 案例），缺失的是「与案例挂钩」的证据</t>
+          <t>L1：语料层面。六类风险在 36 篇语料中均有标注（不含 held-out 案例），缺失的是「与案例挂钩」的证据</t>
         </is>
       </c>
     </row>
@@ -4426,10 +4414,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.966</v>
+        <v>0.931</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.966</v>
+        <v>0.931</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -4444,10 +4432,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.779</v>
+        <v>0.819</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.779</v>
+        <v>0.721</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -4471,7 +4459,7 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk=14; Political Risk=5; Supply Chain Risk=11; Regulatory Risk=10; Market Access Risk=14; Operational Risk=7</t>
+          <t>Trade Risk=16; Political Risk=8; Supply Chain Risk=13; Regulatory Risk=12; Market Access Risk=19; Operational Risk=7</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/risk_assessment_checklist.xlsx
+++ b/data/evaluation/risk_assessment_checklist.xlsx
@@ -1780,7 +1780,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1789,16 +1789,12 @@
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk</t>
-        </is>
-      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1824,21 +1820,25 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="10">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2711,14 +2711,14 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Market Access Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="29">
@@ -2744,25 +2744,29 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr"/>
+          <t>Operational Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="30">
@@ -2788,25 +2792,29 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
+          <t>Operational Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="31">
@@ -2832,7 +2840,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2847,14 +2855,14 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Trade Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="32">
@@ -2880,25 +2888,29 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr"/>
+          <t>Operational Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="33">
@@ -2924,7 +2936,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2939,14 +2951,14 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Trade Risk</t>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="34">
@@ -2972,7 +2984,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2987,14 +2999,14 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="35">
@@ -3020,29 +3032,29 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Trade Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Political Risk; Trade Risk</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk</t>
+          <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
     </row>
   </sheetData>
@@ -3119,13 +3131,13 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>1</v>
+        <v>0.857</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>3</v>
@@ -3141,13 +3153,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -3203,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -3228,7 +3240,7 @@
         <v>0.5</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -3418,7 +3430,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -3583,7 +3595,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -3638,7 +3650,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4133,7 +4145,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4158,7 +4170,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -4324,10 +4336,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.819</v>
+        <v>0.779</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.721</v>
+        <v>0.681</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -4342,10 +4354,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.553</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.652</v>
+        <v>0.626</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -4360,10 +4372,10 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -4378,10 +4390,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -4403,7 +4415,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>L1：语料层面。六类风险在 36 篇语料中均有标注（不含 held-out 案例），缺失的是「与案例挂钩」的证据</t>
+          <t>L1：语料层面。六类风险在 49 篇语料中均有标注（不含 held-out 案例），缺失的是「与案例挂钩」的证据</t>
         </is>
       </c>
     </row>
@@ -4414,10 +4426,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.931</v>
+        <v>0.912</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.931</v>
+        <v>0.912</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -4432,10 +4444,10 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.819</v>
+        <v>0.779</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.721</v>
+        <v>0.681</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -4459,7 +4471,7 @@
       <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk=16; Political Risk=8; Supply Chain Risk=13; Regulatory Risk=12; Market Access Risk=19; Operational Risk=7</t>
+          <t>Trade Risk=20; Political Risk=9; Supply Chain Risk=21; Regulatory Risk=15; Market Access Risk=24; Operational Risk=13</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/risk_assessment_checklist.xlsx
+++ b/data/evaluation/risk_assessment_checklist.xlsx
@@ -4035,7 +4035,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K14" s="2" t="n">
@@ -4426,10 +4426,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.912</v>
+        <v>0.926</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.912</v>
+        <v>0.926</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>

--- a/data/evaluation/risk_assessment_checklist.xlsx
+++ b/data/evaluation/risk_assessment_checklist.xlsx
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1829,16 +1829,12 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Regulatory Risk</t>
-        </is>
-      </c>
+      <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2088,7 +2084,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2101,12 +2097,16 @@
           <t>Political Risk</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2195,14 +2195,14 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
@@ -2792,29 +2792,25 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
@@ -3153,13 +3149,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0</v>
@@ -3375,7 +3371,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -3400,7 +3396,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
@@ -4336,7 +4332,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.779</v>
+        <v>0.799</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>0.681</v>
@@ -4354,10 +4350,10 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.553</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.626</v>
+        <v>0.61</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
@@ -4372,7 +4368,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>18</v>
@@ -4393,7 +4389,7 @@
         <v>30</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -4426,10 +4422,10 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.926</v>
+        <v>0.946</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.926</v>
+        <v>0.946</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -4444,7 +4440,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.779</v>
+        <v>0.799</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>0.681</v>

--- a/data/evaluation/risk_assessment_checklist.xlsx
+++ b/data/evaluation/risk_assessment_checklist.xlsx
@@ -10,12 +10,14 @@
     <sheet name="Checklist" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Results" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="By Risk Category" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Per-Dimension Probe" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="FP Attribution" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Per-Dimension Probe" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$J$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Results'!$A$1:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Results'!$A$1:$K$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FP Attribution'!$A$1:$G$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +39,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +61,11 @@
         <fgColor rgb="007A3E9D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009C5700"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -72,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -84,6 +91,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1414,12 +1424,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
@@ -1427,6 +1437,7 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1480,6 +1491,11 @@
           <t>risk_precision</t>
         </is>
       </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>cited_evidence</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1528,6 +1544,11 @@
       <c r="J2" s="2" t="n">
         <v>0.4</v>
       </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; EU_003; TRD_001; CASE_001; MOFCOM_001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1576,36 +1597,41 @@
       <c r="J3" s="2" t="n">
         <v>0.5</v>
       </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; TRD_001; EU_003; TRD_003; CASE_001</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RELOC_002</t>
+          <t>RELOC_001</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>长安汽车 Changan Automobile</t>
+          <t>比亚迪 BYD</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+          <t>Market Access Risk; Political Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+          <t>Market Access Risk; Political Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -1618,7 +1644,12 @@
         <v>1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0002; EVD-IRS_001-C0000; EVD-CASE_008-C0000</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1634,7 +1665,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>optimized</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1644,128 +1675,143 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; CASE_001; CASE_004; MOFCOM_001</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>RELOC_002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech</t>
+          <t>长安汽车 Changan Automobile</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>optimized</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; CASE_001; CASE_004; CASE_008</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RELOC_003</t>
+          <t>RELOC_002</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>国轩高科 Gotion High-Tech</t>
+          <t>长安汽车 Changan Automobile</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>optimized</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-XPEV_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0002; EVD-IRS_001-C0000; EVD-CASE_008-C0001</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>RELOC_003</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy</t>
+          <t>国轩高科 Gotion High-Tech</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1775,37 +1821,46 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; WB_001</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RELOC_004</t>
+          <t>RELOC_003</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>亿纬锂能 EVE Energy</t>
+          <t>国轩高科 Gotion High-Tech</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1815,86 +1870,100 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
+          <t>Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; WB_001; CASE_001; CASE_008</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>RELOC_003</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda</t>
+          <t>国轩高科 Gotion High-Tech</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0028; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>RELOC_004</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda</t>
+          <t>亿纬锂能 EVE Energy</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>optimized</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1920,108 +1989,115 @@
       <c r="J11" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; CASE_007; WB_001; CASE_001</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RELOC_004</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT</t>
+          <t>亿纬锂能 EVE Energy</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>optimized</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Regulatory Risk; Supply Chain Risk</t>
-        </is>
-      </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.6</v>
+        <v>1</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; CASE_007; WB_001; CASE_001</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RELOC_004</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT</t>
+          <t>亿纬锂能 EVE Energy</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>optimized</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Market Access Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-TRD_003-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-CASE_010-C0003; EVD-CASE_007-C0001; EVD-WB_001-C0000</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>RELOC_007</t>
+          <t>RELOC_005</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt</t>
+          <t>欣旺达 Sunwoda</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2031,7 +2107,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2041,35 +2117,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; WB_001</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RELOC_007</t>
+          <t>RELOC_005</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt</t>
+          <t>欣旺达 Sunwoda</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2079,103 +2156,101 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk; Regulatory Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4</v>
+        <v>1</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; WB_001; CASE_001; CASE_008</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>RELOC_005</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material</t>
+          <t>欣旺达 Sunwoda</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+          <t>Market Access Risk; Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>RELOC_006</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material</t>
+          <t>蜂巢能源 SVOLT</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>optimized</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2185,131 +2260,138 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+          <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; MOFCOM_001; CASE_001; CASE_004; TRD_003</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001</t>
+          <t>RELOC_006</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL</t>
+          <t>蜂巢能源 SVOLT</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>optimized</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; TRD_003; CASE_001; CASE_004; CASE_008</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001</t>
+          <t>RELOC_006</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL</t>
+          <t>蜂巢能源 SVOLT</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>optimized</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk; Regulatory Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.5</v>
       </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-CASE_008-C0000; EVD-WB_001-C0000</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_002</t>
+          <t>RELOC_007</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL</t>
+          <t>华友钴业 Huayou Cobalt</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2319,12 +2401,12 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Political Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2334,30 +2416,35 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Market Access Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; WB_001; MOFCOM_001; CASE_001; CASE_008</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_002</t>
+          <t>RELOC_007</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL</t>
+          <t>华友钴业 Huayou Cobalt</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2367,12 +2454,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Political Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2382,214 +2469,239 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Market Access Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; WB_001; CASE_001; CASE_008; MOFCOM_001</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_003</t>
+          <t>RELOC_007</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD</t>
+          <t>华友钴业 Huayou Cobalt</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+          <t>Political Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+          <t>Political Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Market Access Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0002; EVD-WTO_004-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0002; EVD-WB_001-C0000; EVD-CASE_008-C0000; EVD-CASE_007-C0003</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_003</t>
+          <t>RELOC_008</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD</t>
+          <t>中伟股份 CNGR Advanced Material</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>optimized</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
+          <t>Operational Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; WB_001; CASE_001; MOFCOM_001; CASE_008</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_004</t>
+          <t>RELOC_008</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar</t>
+          <t>中伟股份 CNGR Advanced Material</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>optimized</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Political Risk; Regulatory Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Political Risk; Regulatory Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>TRD_001; WB_001; CASE_001; CASE_008; MOFCOM_001</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_004</t>
+          <t>RELOC_008</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar</t>
+          <t>中伟股份 CNGR Advanced Material</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>optimized</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Political Risk; Regulatory Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk; Regulatory Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>0.5</v>
       </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0002; EVD-WTO_004-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000; EVD-TSLA_001-C0000</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_005</t>
+          <t>PLUS1_001</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics</t>
+          <t>宁德时代 CATL</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2599,7 +2711,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2609,12 +2721,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2623,21 +2735,26 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; CASE_010; CASE_001; CASE_008; WH_002</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_005</t>
+          <t>PLUS1_001</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics</t>
+          <t>宁德时代 CATL</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2647,7 +2764,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2657,12 +2774,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2671,205 +2788,230 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; CASE_010; CASE_001; CASE_008; TSLA_001</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>PLUS1_001</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+          <t>宁德时代 CATL</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-ALB_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0021; EVD-CASE_008-C0001; EVD-DHS_001-C0000; EVD-CASE_007-C0003</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>PLUS1_002</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+          <t>宁德时代 CATL</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>optimized</t>
+          <t>baseline</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Regulatory Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
+          <t>Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; CASE_010; CASE_001; CASE_008; TSLA_001</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>PLUS1_002</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+          <t>宁德时代 CATL</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>optimized</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
+          <t>Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>0.5</v>
       </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; CASE_010; CASE_001; CASE_008; TSLA_001</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>PLUS1_002</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+          <t>宁德时代 CATL</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>optimized</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Regulatory Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>0.667</v>
       </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-WTO_004-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>PLUS1_003</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）</t>
+          <t>比亚迪 BYD</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2879,45 +3021,46 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; CASE_010; CASE_008; CASE_001; EU_003</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>PLUS1_003</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）</t>
+          <t>比亚迪 BYD</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2927,134 +3070,1022 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; CASE_010; CASE_008; CASE_001; TSLA_001</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>PLUS1_003</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+          <t>比亚迪 BYD</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>risk_dimension</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Political Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk; Supply Chain Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0002; EVD-WTO_004-C0000; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-ALB_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0002; EVD-IRS_001-C0000; EVD-WB_001-C0000</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>PLUS1_004</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源 JinkoSolar</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Political Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; CASE_003; TRD_001; WH_002; CASE_007</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_004</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源 JinkoSolar</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>optimized</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Political Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; CASE_003; TRD_001; CASE_007; WH_002</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_004</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源 JinkoSolar</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>risk_dimension</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Political Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-TRD_003-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-ITA_001-C0000; EVD-CASE_010-C0003; EVD-EU_001-C0000; EVD-WB_001-C0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_005</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>三星电子 Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; CASE_008; CASE_001; CASE_003; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_005</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>三星电子 Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>optimized</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>CASE_010; CASE_001; CASE_008; TSLA_001; CASE_003</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_005</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>三星电子 Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>risk_dimension</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-TRD_003-C0000; EVD-WEF_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0133; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_001</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; DHS_001; CASE_008; EU_003; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_001</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>optimized</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Regulatory Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; DHS_001; CASE_008; CASE_004; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_001</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>risk_dimension</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-TRD_003-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-CASE_010-C0003; EVD-CASE_007-C0001; EVD-WB_001-C0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>DHS_001; CASE_001; CASE_008; EU_003; CNGOV_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>optimized</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Regulatory Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; DHS_001; CASE_008; CASE_004; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>risk_dimension</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-TRD_003-C0000; EVD-WTO_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0021; EVD-WB_001-C0000; EVD-CASE_008-C0001; EVD-CASE_001-C0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_003</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>制造业外迁企业（行业层面）</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; DHS_001; EU_003; SNE_001; CASE_010</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_003</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>制造业外迁企业（行业层面）</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>optimized</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; DHS_001; EU_003; SNE_001; CASE_008</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_003</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>制造业外迁企业（行业层面）</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>risk_dimension</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0001; EVD-TRD_003-C0000; EVD-CASE_001-C0000; EVD-NIO_001-C0000; EVD-BIS_002-C0000; EVD-MOFCOM_001-C0169; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-EU_003-C0000; EVD-WB_001-C0000; EVD-DHS_001-C0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>RETURN_004</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>蜂巢能源 SVOLT（欧洲业务）</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>baseline</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; DHS_001; CASE_008; EU_003; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>optimized</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Operational Risk; Political Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Operational Risk; Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Operational Risk</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>Political Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
+      <c r="I51" s="2" t="n">
         <v>0.333</v>
       </c>
-      <c r="J35" s="2" t="n">
+      <c r="J51" s="2" t="n">
         <v>0.333</v>
       </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>CASE_001; DHS_001; CASE_008; CASE_004; SNE_001</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>risk_dimension</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk; Political Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0002; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-TSLA_001-C0000; EVD-CASE_008-C0000; EVD-WB_001-C0000</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J35"/>
+  <autoFilter ref="A1:K52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3065,16 +4096,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3100,15 +4133,25 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>identified_risk_dimension</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>recall_baseline</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>recall_optimized</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>recall_risk_dimension</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>over_claimed_cases</t>
         </is>
@@ -3130,12 +4173,18 @@
         <v>12</v>
       </c>
       <c r="E2" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.857</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3155,14 +4204,20 @@
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" s="2" t="n">
         <v>0.1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="H3" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3180,12 +4235,18 @@
         <v>11</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3205,12 +4266,18 @@
         <v>0</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3230,12 +4297,18 @@
         <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3255,12 +4328,18 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3270,6 +4349,3656 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G98"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>risk_category</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>case_annotation</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>confirming_evidence_ids</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>confirming_publishers</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_001</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_001</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; SNE_001</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; SNE Research</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_001</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_001</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WH_002; IRS_001</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_001</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; CASE_008</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 中国基金报</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>案例标注为 Optional，不计入 missing / false positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_002</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>长安汽车 Changan Automobile</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_002</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>长安汽车 Changan Automobile</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_002</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>长安汽车 Changan Automobile</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; WTO_001</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_002</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>长安汽车 Changan Automobile</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; MOFCOM_001; MOFCOM_002; BIS_002</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 小鹏汽车（XPeng Inc.，SEC EDGAR）; 商务部、海关总署; 商务部</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_002</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>长安汽车 Changan Automobile</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WH_002; IRS_001</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_002</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>长安汽车 Changan Automobile</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>CASE_008</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>中国基金报</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_003</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>国轩高科 Gotion High-Tech</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_003</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>国轩高科 Gotion High-Tech</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_003</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>国轩高科 Gotion High-Tech</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; WTO_001</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_003</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>国轩高科 Gotion High-Tech</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_003</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>国轩高科 Gotion High-Tech</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WH_002; IRS_001</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_003</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>国轩高科 Gotion High-Tech</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_008</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 中国基金报</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>案例标注为 Optional，不计入 missing / false positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_004</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>亿纬锂能 EVE Energy</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_004</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>亿纬锂能 EVE Energy</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_004</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>亿纬锂能 EVE Energy</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; BIS_002; XPEV_001</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 美国商务部工业与安全局（BIS）</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_004</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>亿纬锂能 EVE Energy</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WH_002; CASE_010; CASE_003</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）; 美国商务部（经律所解读）</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_004</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>亿纬锂能 EVE Energy</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>CASE_007; WB_001</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; 世界银行（World Bank）</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_005</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>欣旺达 Sunwoda</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_005</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>欣旺达 Sunwoda</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_005</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>欣旺达 Sunwoda</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; WTO_001</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_005</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>欣旺达 Sunwoda</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_005</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>欣旺达 Sunwoda</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WH_002; IRS_001</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_005</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>欣旺达 Sunwoda</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_008</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 中国基金报</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_006</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_006</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_006</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; ALB_001</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_006</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; BIS_002; XPEV_001</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 美国商务部工业与安全局（BIS）</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_006</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WH_002; IRS_001</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_006</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>CASE_008; WB_001</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>中国基金报; 世界银行（World Bank）</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_007</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>华友钴业 Huayou Cobalt</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_007</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>华友钴业 Huayou Cobalt</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004; WEF_001</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）; 世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_007</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>华友钴业 Huayou Cobalt</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; ALB_001; WTO_001</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_007</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>华友钴业 Huayou Cobalt</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; BIS_002; XPEV_001</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 美国商务部工业与安全局（BIS）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_007</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>华友钴业 Huayou Cobalt</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WTO_004; IRS_001; WH_002</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_007</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>华友钴业 Huayou Cobalt</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_008; CASE_007</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 中国基金报; C114通信网</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>案例标注为 Optional，不计入 missing / false positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_008</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>中伟股份 CNGR Advanced Material</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Trade Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_008</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>中伟股份 CNGR Advanced Material</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004; WEF_001</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）; 世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_008</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>中伟股份 CNGR Advanced Material</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; ALB_001; WTO_001</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_008</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>中伟股份 CNGR Advanced Material</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; BIS_002; XPEV_001</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 美国商务部工业与安全局（BIS）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_008</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>中伟股份 CNGR Advanced Material</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WTO_004; WH_002; IRS_001</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RELOC_008</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>中伟股份 CNGR Advanced Material</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_008; TSLA_001</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 中国基金报; 特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_001</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>DOC_001; CASE_002; CASE_003; WH_002</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_001</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_001</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; SNE_001; ALB_001</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; SNE Research; 雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_001</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_001</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; IRS_001; WH_002</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_001</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; CASE_008; DHS_001; CASE_007</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 中国基金报; 美国国土安全部（DHS，Federal Register）; C114通信网</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>案例标注为 Optional，不计入 missing / false positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_002</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>DOC_001; CASE_002; CASE_003; WH_002</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_002</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004; WEF_001</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）; 世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_002</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; SNE_001; WTO_001</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; SNE Research; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_002</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; BIS_002; XPEV_001</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 美国商务部工业与安全局（BIS）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_002</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WTO_004; IRS_001</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_002</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>宁德时代 CATL</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>SNE_001; WB_001; CASE_008</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>SNE Research; 世界银行（World Bank）; 中国基金报</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>案例标注为 Optional，不计入 missing / false positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_003</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_003</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_003</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; SNE_001; ALB_001</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; SNE Research; 雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_003</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_003</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WTO_004; WH_002; IRS_001</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_003</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>比亚迪 BYD</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; SNE_001</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; SNE Research</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_004</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源 JinkoSolar</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_004</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源 JinkoSolar</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_004</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源 JinkoSolar</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_002; ITA_001</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 美国国际贸易管理局（ITA）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_004</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源 JinkoSolar</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>CASE_003; CASE_010; EU_001</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国白宫（经律所解读）; 欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_004</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>晶科能源 JinkoSolar</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>案例标注为 Optional，不计入 missing / false positive</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_005</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>三星电子 Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>CASE_002; CASE_003; DOC_001; CASE_010; TRD_003</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_005</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>三星电子 Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_005</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>三星电子 Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; WTO_001</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_005</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>三星电子 Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_005</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>三星电子 Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WH_002; IRS_001</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>PLUS1_005</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>三星电子 Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_008</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 中国基金报</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_001</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_001</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_001</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_001</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WH_002; CASE_003; CASE_010</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国商务部（经律所解读）; 美国白宫（经律所解读）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_001</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>CASE_007; WB_001</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>C114通信网; 世界银行（World Bank）</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>CASE_002; DOC_001; CASE_003; TRD_003; WTO_003</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国商务部; 联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Trade Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; ALB_001; WTO_001</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; IRS_001; WH_002</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_002</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_008; CASE_001</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 中国基金报; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_003</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>制造业外迁企业（行业层面）</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>CASE_003; CASE_002; WH_002; CASE_010; TRD_003</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Trade Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_003</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>制造业外迁企业（行业层面）</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; CASE_001</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_003</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>制造业外迁企业（行业层面）</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; BIS_002; MOFCOM_001; MOFCOM_002; XPEV_001</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 美国商务部工业与安全局（BIS）; 商务部、海关总署; 商务部</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_003</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>制造业外迁企业（行业层面）</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>WH_002; CASE_010; EU_003</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）; 欧盟委员会（EUR-Lex / Official Journal）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_003</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>制造业外迁企业（行业层面）</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>WB_001; CASE_001; DHS_001</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>世界银行（World Bank）; 路透社（Reuters）; 美国国土安全部（DHS，Federal Register）</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>DOC_001; CASE_002; CASE_003; CASE_010</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫（经律所解读）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>WEF_001</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>世界经济论坛（WEF）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; ALB_001; WTO_001</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; WH_002; IRS_001</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001; CASE_008; WB_001</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）; 中国基金报; 世界银行（World Bank）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G98"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4288,19 +9017,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="78" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4321,6 +9051,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Risk-dimension (P0)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
@@ -4337,7 +9072,10 @@
       <c r="C2" s="2" t="n">
         <v>0.681</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>应识别风险中有多少被证据链覆盖</t>
         </is>
@@ -4355,7 +9093,10 @@
       <c r="C3" s="2" t="n">
         <v>0.61</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>识别出的风险中有多少属于本题期望风险</t>
         </is>
@@ -4373,7 +9114,10 @@
       <c r="C4" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>期望风险中未被证据覆盖的次数</t>
         </is>
@@ -4391,7 +9135,10 @@
       <c r="C5" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>不属于该题却被识别的风险次数</t>
         </is>
@@ -4409,7 +9156,10 @@
       <c r="C6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>L1：语料层面。六类风险在 49 篇语料中均有标注（不含 held-out 案例），缺失的是「与案例挂钩」的证据</t>
         </is>
@@ -4427,16 +9177,19 @@
       <c r="C7" s="2" t="n">
         <v>0.946</v>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>L2：检索层面。按风险维度单独提问时的覆盖上限；不是现行产品行为</t>
+      <c r="D7" s="2" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>L2：检索层面。按风险维度单独提问时的覆盖上界；P0 之后已由产品实现达到</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>风险识别覆盖（现行单次检索）</t>
+          <t>风险识别覆盖（现行产品行为）</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -4445,9 +9198,12 @@
       <c r="C8" s="2" t="n">
         <v>0.681</v>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>L3：现行产品行为。差距 = L1 - L3，定位在「检索策略」而非「语料」</t>
+      <c r="D8" s="2" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>L3：开启 RISK_DIMENSION_RETRIEVAL（默认）后走 Risk-dimension 列；差距 = L1 - L3</t>
         </is>
       </c>
     </row>
@@ -4456,6 +9212,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -4465,7 +9222,8 @@
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Trade Risk=20; Political Risk=9; Supply Chain Risk=21; Regulatory Risk=15; Market Access Risk=24; Operational Risk=13</t>
         </is>
@@ -4476,6 +9234,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -4485,9 +9244,10 @@
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>identified_risks = Top-5 引用证据在 Task 1 schema 中的 related_risk 并集；expected = 案例记录的人工标注 related_risk（已归并到 Task 1 六类词表）</t>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>identified_risks = 引用证据在 Task 1 schema 中的 related_risk 并集；expected = 案例记录的人工标注 related_risk（已归并到 Task 1 六类词表）。risk_dimension 列：六个风险维度各检索 Top-5，只保留 related_risk 标签确认过的条目</t>
         </is>
       </c>
     </row>
@@ -4499,9 +9259,10 @@
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk 记为 Optional，不计入 missing / false positive；本评测测的是证据链能否支撑风险识别，不是 LLM 生成风险的质量</t>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk 记为 Optional，不计入 missing / false positive；本评测测的是证据链能否支撑风险识别，不是 LLM 生成风险的质量。risk_dimension 的 Precision 低于基线主要是口径效应：39 次误报里 Regulatory 14 次、Market Access 11 次，均可追溯到中国侧出口管制 / 公司披露与欧盟法规证据；逐条归因见 FP Attribution sheet</t>
         </is>
       </c>
     </row>

--- a/data/evaluation/risk_assessment_checklist.xlsx
+++ b/data/evaluation/risk_assessment_checklist.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Checklist'!$A$1:$J$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Results'!$A$1:$K$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FP Attribution'!$A$1:$G$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FP Attribution'!$A$1:$G$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1520,33 +1520,29 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Political Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; EU_003; TRD_001; CASE_001; MOFCOM_001</t>
+          <t>SNE_001; EU_003; TRD_001; MOFCOM_003; CASE_004</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1644,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0002; EVD-IRS_001-C0000; EVD-CASE_008-C0000</t>
+          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-MOFCOM_005-C0000; EVD-MOFCOM_006-C0152; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0002; EVD-IRS_001-C0000; EVD-CASE_008-C0000</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1671,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1686,18 +1682,18 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Supply Chain Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_001; CASE_004; MOFCOM_001</t>
+          <t>TRD_001; MOFCOM_003; CASE_004; TRD_003; NIO_001</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1795,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-XPEV_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0002; EVD-IRS_001-C0000; EVD-CASE_008-C0001</t>
+          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-MOFCOM_005-C0000; EVD-MOFCOM_006-C0003; EVD-MOFCOM_003-C0088; EVD-MOFCOM_004-C0004; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-NIO_001-C0000; EVD-XPEV_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0002; EVD-WTO_004-C0000; EVD-CASE_008-C0001; EVD-TSLA_001-C0000</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1822,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1837,18 +1833,18 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; WB_001</t>
+          <t>MOFCOM_003; TRD_001; CASE_001; MOFCOM_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -1875,29 +1871,29 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Market Access Risk</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
+          <t>Market Access Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.667</v>
+        <v>0.6</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; WB_001; CASE_001; CASE_008</t>
+          <t>TRD_001; TRD_003; WB_001; CASE_001; MOFCOM_001</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1942,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0028; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000</t>
+          <t>EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-MOFCOM_005-C0000; EVD-MOFCOM_003-C0088; EVD-MOFCOM_004-C0004; EVD-TRD_003-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0028; EVD-WTO_004-C0000; EVD-CASE_008-C0000; EVD-CASE_007-C0003</t>
         </is>
       </c>
     </row>
@@ -1973,25 +1969,33 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
+          <t>Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Operational Risk</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk; Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; CASE_007; WB_001; CASE_001</t>
+          <t>TRD_001; MOFCOM_004; MOFCOM_003; TRD_003; MOFCOM_006</t>
         </is>
       </c>
     </row>
@@ -2063,7 +2067,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2074,18 +2078,18 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk</t>
+          <t>Market Access Risk; Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-TRD_003-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-CASE_010-C0003; EVD-CASE_007-C0001; EVD-WB_001-C0000</t>
+          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-MOFCOM_005-C0000; EVD-MOFCOM_004-C0004; EVD-TRD_003-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-CASE_007-C0001</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2116,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2123,7 +2127,7 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk</t>
+          <t>Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -2134,7 +2138,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; MOFCOM_001; CASE_001; WB_001</t>
+          <t>MOFCOM_003; TRD_001; MOFCOM_005; CASE_001; TRD_003</t>
         </is>
       </c>
     </row>
@@ -2161,25 +2165,29 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk; Regulatory Risk</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; TRD_003; WB_001; CASE_001; CASE_008</t>
+          <t>TRD_001; TRD_003; WB_001; CASE_001; MOFCOM_001</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2236,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000</t>
+          <t>EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-MOFCOM_005-C0000; EVD-MOFCOM_003-C0088; EVD-MOFCOM_004-C0004; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0021; EVD-CASE_008-C0000</t>
         </is>
       </c>
     </row>
@@ -2255,29 +2263,33 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
+          <t>Operational Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk; Supply Chain Risk</t>
+          <t>Political Risk; Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; MOFCOM_001; CASE_001; CASE_004; TRD_003</t>
+          <t>TRD_001; MOFCOM_003; CASE_004; MOFCOM_004; CASE_001</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2391,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-CASE_008-C0000; EVD-WB_001-C0000</t>
+          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-MOFCOM_005-C0128; EVD-MOFCOM_006-C0003; EVD-MOFCOM_003-C0088; EVD-MOFCOM_004-C0004; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-CASE_008-C0000</t>
         </is>
       </c>
     </row>
@@ -2406,33 +2418,29 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Political Risk; Supply Chain Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; WB_001; MOFCOM_001; CASE_001; CASE_008</t>
+          <t>MOFCOM_003; TRD_001; WB_001; CASE_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2542,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0002; EVD-WTO_004-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0002; EVD-WB_001-C0000; EVD-CASE_008-C0000; EVD-CASE_007-C0003</t>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0002; EVD-MOFCOM_005-C0000; EVD-MOFCOM_003-C0088; EVD-MOFCOM_004-C0004; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-WTO_004-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0002; EVD-CASE_008-C0000; EVD-WB_001-C0000</t>
         </is>
       </c>
     </row>
@@ -2561,33 +2569,29 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+          <t>Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; WB_001; CASE_001; MOFCOM_001; CASE_008</t>
+          <t>MOFCOM_003; TRD_001; WB_001; CASE_001; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2618,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Operational Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2629,18 +2633,18 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
         <v>0.667</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.4</v>
+        <v>0.667</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>TRD_001; WB_001; CASE_001; CASE_008; MOFCOM_001</t>
+          <t>TRD_001; WB_001; CASE_001; TRD_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2693,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0002; EVD-WTO_004-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000; EVD-TSLA_001-C0000</t>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0002; EVD-MOFCOM_005-C0000; EVD-MOFCOM_003-C0088; EVD-MOFCOM_004-C0004; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WTO_004-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0021; EVD-CASE_008-C0000; EVD-WB_001-C0000</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2746,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; CASE_010; CASE_001; CASE_008; WH_002</t>
+          <t>SNE_001; CASE_010; CASE_008; CASE_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2848,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-ALB_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0021; EVD-CASE_008-C0001; EVD-DHS_001-C0000; EVD-CASE_007-C0003</t>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-TRD_003-C0000; EVD-MOFCOM_005-C0000; EVD-MOFCOM_003-C0001; EVD-MOFCOM_004-C0004; EVD-SNE_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0021; EVD-CASE_008-C0001; EVD-DHS_001-C0000</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2901,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; CASE_010; CASE_001; CASE_008; TSLA_001</t>
+          <t>SNE_001; CASE_010; CASE_008; CASE_001; CASE_002</t>
         </is>
       </c>
     </row>
@@ -2999,7 +3003,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-WTO_004-C0000; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000</t>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-MOFCOM_005-C0000; EVD-MOFCOM_003-C0001; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-EU_001-C0000; EVD-WTO_004-C0000; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3052,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; CASE_010; CASE_008; CASE_001; EU_003</t>
+          <t>SNE_001; CASE_010; EU_003; CASE_008; CASE_001</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3150,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0002; EVD-WTO_004-C0000; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-ALB_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0002; EVD-IRS_001-C0000; EVD-WB_001-C0000</t>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0002; EVD-MOFCOM_005-C0000; EVD-TRD_003-C0000; EVD-SNE_001-C0000; EVD-ALB_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WTO_004-C0000; EVD-WH_002-C0002; EVD-IRS_001-C0000; EVD-CASE_008-C0000; EVD-WB_001-C0000</t>
         </is>
       </c>
     </row>
@@ -3173,33 +3177,29 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk; Regulatory Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Political Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_003; TRD_001; WH_002; CASE_007</t>
+          <t>CASE_010; CASE_003; MOFCOM_004; CASE_007; TRD_001</t>
         </is>
       </c>
     </row>
@@ -3279,33 +3279,29 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Market Access Risk; Political Risk; Regulatory Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-TRD_003-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-ITA_001-C0000; EVD-CASE_010-C0003; EVD-EU_001-C0000; EVD-WB_001-C0000</t>
+          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-MOFCOM_004-C0004; EVD-MOFCOM_005-C0000; EVD-TRD_003-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-ITA_001-C0000; EVD-BIS_002-C0000; EVD-MOFCOM_001-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WB_001-C0000</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3354,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_008; CASE_001; CASE_003; SNE_001</t>
+          <t>CASE_010; CASE_008; CASE_001; TSLA_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3407,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>CASE_010; CASE_001; CASE_008; TSLA_001; CASE_003</t>
+          <t>CASE_010; CASE_001; CASE_008; TSLA_001; SNE_001</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3456,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-TRD_003-C0000; EVD-WEF_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0133; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-WB_001-C0000; EVD-CASE_008-C0000</t>
+          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-TRD_003-C0000; EVD-WH_002-C0000; EVD-MOFCOM_005-C0000; EVD-MOFCOM_003-C0088; EVD-MOFCOM_004-C0004; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0133; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0021; EVD-CASE_008-C0000</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3483,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -3498,18 +3494,18 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk</t>
+          <t>Market Access Risk; Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; DHS_001; CASE_008; EU_003; SNE_001</t>
+          <t>DHS_001; CASE_001; MOFCOM_005; EU_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3585,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3600,18 +3596,18 @@
       <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Regulatory Risk</t>
+          <t>Market Access Risk; Political Risk; Regulatory Risk</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-TRD_003-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-CASE_010-C0003; EVD-CASE_007-C0001; EVD-WB_001-C0000</t>
+          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-MOFCOM_005-C0000; EVD-MOFCOM_004-C0004; EVD-TRD_003-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-CASE_007-C0001</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3656,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>DHS_001; CASE_001; CASE_008; EU_003; CNGOV_001</t>
+          <t>DHS_001; CASE_001; MOFCOM_005; EU_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -3740,33 +3736,29 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-TRD_003-C0000; EVD-WTO_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0021; EVD-WB_001-C0000; EVD-CASE_008-C0001; EVD-CASE_001-C0000</t>
+          <t>EVD-CASE_002-C0000; EVD-DOC_001-C0000; EVD-CASE_003-C0000; EVD-USMCA_001-C0000; EVD-MOFCOM_005-C0000; EVD-MOFCOM_003-C0088; EVD-MOFCOM_004-C0004; EVD-MOFCOM_006-C0152; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-IRS_001-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-CASE_008-C0001</t>
         </is>
       </c>
     </row>
@@ -3793,33 +3785,29 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; DHS_001; EU_003; SNE_001; CASE_010</t>
+          <t>CASE_001; DHS_001; MOFCOM_004; MOFCOM_005; EU_003</t>
         </is>
       </c>
     </row>
@@ -3899,33 +3887,29 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Supply Chain Risk</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Political Risk; Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Regulatory Risk; Trade Risk</t>
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>EVD-CASE_003-C0000; EVD-CASE_002-C0000; EVD-WH_002-C0000; EVD-CASE_010-C0001; EVD-TRD_003-C0000; EVD-CASE_001-C0000; EVD-NIO_001-C0000; EVD-BIS_002-C0000; EVD-MOFCOM_001-C0169; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-EU_003-C0000; EVD-WB_001-C0000; EVD-DHS_001-C0000</t>
+          <t>EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0001; EVD-WH_002-C0000; EVD-TRD_003-C0000; EVD-MOFCOM_004-C0069; EVD-CASE_001-C0000; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0169; EVD-BIS_002-C0000; EVD-XPEV_001-C0000; EVD-WB_001-C0000</t>
         </is>
       </c>
     </row>
@@ -3952,33 +3936,29 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk; Operational Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
+          <t>Market Access Risk; Operational Risk; Political Risk; Regulatory Risk; Supply Chain Risk; Trade Risk</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk; Trade Risk</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Political Risk</t>
-        </is>
-      </c>
+          <t>Operational Risk; Political Risk; Trade Risk</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Market Access Risk; Regulatory Risk; Supply Chain Risk</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>CASE_001; DHS_001; CASE_008; EU_003; SNE_001</t>
+          <t>DHS_001; CASE_001; MOFCOM_005; EU_003; CASE_008</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4060,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0002; EVD-WEF_001-C0000; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_001-C0000; EVD-MOFCOM_002-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-WH_002-C0021; EVD-IRS_001-C0000; EVD-TSLA_001-C0000; EVD-CASE_008-C0000; EVD-WB_001-C0000</t>
+          <t>EVD-DOC_001-C0000; EVD-CASE_002-C0000; EVD-CASE_003-C0000; EVD-CASE_010-C0002; EVD-MOFCOM_005-C0128; EVD-MOFCOM_003-C0088; EVD-MOFCOM_004-C0004; EVD-TRD_003-C0000; EVD-ALB_001-C0000; EVD-WTO_001-C0082; EVD-NIO_001-C0000; EVD-MOFCOM_002-C0000; EVD-MOFCOM_001-C0000; EVD-XPEV_001-C0000; EVD-BIS_002-C0000; EVD-EU_001-C0000; EVD-IRS_001-C0000; EVD-WH_002-C0021; EVD-TSLA_001-C0000; EVD-CASE_008-C0000</t>
         </is>
       </c>
     </row>
@@ -4198,25 +4178,25 @@
         <v>10</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -4260,7 +4240,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0</v>
@@ -4269,7 +4249,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0</v>
@@ -4278,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -4291,25 +4271,25 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -4322,7 +4302,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>11</v>
@@ -4331,7 +4311,7 @@
         <v>11</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0.909</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1</v>
@@ -4354,7 +4334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4463,12 +4443,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_005; MOFCOM_006</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -4537,12 +4517,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4685,12 +4665,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_005; MOFCOM_006; MOFCOM_003; MOFCOM_004</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4722,12 +4702,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WTO_001</t>
+          <t>TRD_003; ALB_001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4759,12 +4739,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; XPEV_001; MOFCOM_001; MOFCOM_002; BIS_002</t>
+          <t>NIO_001; XPEV_001; MOFCOM_002; MOFCOM_001; BIS_002</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 小鹏汽车（XPeng Inc.，SEC EDGAR）; 商务部、海关总署; 商务部</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 小鹏汽车（XPeng Inc.，SEC EDGAR）; 商务部; 商务部、海关总署</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4796,12 +4776,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WH_002; IRS_001</t>
+          <t>EU_001; IRS_001; WH_002; WTO_004</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室; 世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4833,12 +4813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CASE_008</t>
+          <t>CASE_008; TSLA_001</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>中国基金报</t>
+          <t>中国基金报; 特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4870,7 +4850,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
+          <t>CASE_002; CASE_003; DOC_001; CASE_010; WH_002</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4907,12 +4887,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_004</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4981,12 +4961,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5018,12 +4998,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WH_002; IRS_001</t>
+          <t>EU_001; IRS_001; WH_002; WTO_004</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室; 世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5055,12 +5035,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>WB_001; CASE_008</t>
+          <t>CASE_008; CASE_007</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）; 中国基金报</t>
+          <t>中国基金报; C114通信网</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5119,27 +5099,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>MOFCOM_005; MOFCOM_004</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -5156,27 +5136,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; BIS_002; XPEV_001</t>
+          <t>TRD_003; WTO_001</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 美国商务部工业与安全局（BIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5173,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5203,17 +5183,17 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WH_002; CASE_010; CASE_003</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）; 美国商务部（经律所解读）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -5230,44 +5210,44 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; WB_001</t>
+          <t>EU_001; WH_002</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>C114通信网; 世界银行（World Bank）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>RELOC_005</t>
+          <t>RELOC_004</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>欣旺达 Sunwoda</t>
+          <t>亿纬锂能 EVE Energy</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5277,12 +5257,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5304,27 +5284,27 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CASE_002; CASE_003; DOC_001; CASE_010; WH_002</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -5341,27 +5321,27 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WTO_001</t>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_004</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -5378,27 +5358,27 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+          <t>TRD_003; ALB_001</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5395,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -5425,17 +5405,17 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WH_002; IRS_001</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -5452,44 +5432,44 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>WB_001; CASE_008</t>
+          <t>EU_001; IRS_001; WH_002</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）; 中国基金报</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>RELOC_006</t>
+          <t>RELOC_005</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT</t>
+          <t>欣旺达 Sunwoda</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -5499,12 +5479,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -5526,27 +5506,27 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>CASE_002; DOC_001; CASE_003; CASE_010; WH_002</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5543,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -5573,17 +5553,17 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; ALB_001</t>
+          <t>MOFCOM_005; MOFCOM_006; MOFCOM_003; MOFCOM_004</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5580,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -5610,17 +5590,17 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; BIS_002; XPEV_001</t>
+          <t>TRD_003; ALB_001</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 美国商务部工业与安全局（BIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -5637,27 +5617,27 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WH_002; IRS_001</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -5674,7 +5654,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -5684,12 +5664,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CASE_008; WB_001</t>
+          <t>EU_001; WH_002; IRS_001</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>中国基金报; 世界银行（World Bank）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -5701,17 +5681,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RELOC_007</t>
+          <t>RELOC_006</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>华友钴业 Huayou Cobalt</t>
+          <t>蜂巢能源 SVOLT</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -5721,12 +5701,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -5748,7 +5728,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5758,12 +5738,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>WTO_004; WEF_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）; 世界经济论坛（WEF）</t>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5785,7 +5765,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5795,12 +5775,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; ALB_001; WTO_001</t>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_004</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5822,27 +5802,27 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; BIS_002; XPEV_001</t>
+          <t>TRD_003; ALB_001; WTO_001</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 美国商务部工业与安全局（BIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5839,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5869,17 +5849,17 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WTO_004; IRS_001; WH_002</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -5896,64 +5876,64 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>WB_001; CASE_008; CASE_007</t>
+          <t>WTO_004; EU_001; IRS_001; WH_002</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）; 中国基金报; C114通信网</t>
+          <t>世界贸易组织（WTO）; 欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>案例标注为 Optional，不计入 missing / false positive</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RELOC_008</t>
+          <t>RELOC_007</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>中伟股份 CNGR Advanced Material</t>
+          <t>华友钴业 Huayou Cobalt</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
+          <t>CASE_008; WB_001</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）</t>
+          <t>中国基金报; 世界银行（World Bank）</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Trade Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注为 Optional，不计入 missing / false positive</t>
         </is>
       </c>
     </row>
@@ -5970,27 +5950,27 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>WTO_004; WEF_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）; 世界经济论坛（WEF）</t>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Trade Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -6007,7 +5987,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -6017,12 +5997,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; ALB_001; WTO_001</t>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_004</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -6044,27 +6024,27 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; BIS_002; XPEV_001</t>
+          <t>TRD_003; ALB_001; WTO_001</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 美国商务部工业与安全局（BIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6061,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6091,17 +6071,17 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WTO_004; WH_002; IRS_001</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -6118,44 +6098,44 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>WB_001; CASE_008; TSLA_001</t>
+          <t>EU_001; WTO_004; IRS_001; WH_002</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）; 中国基金报; 特斯拉公司（Tesla, Inc.，SEC EDGAR）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_001</t>
+          <t>RELOC_008</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>宁德时代 CATL</t>
+          <t>中伟股份 CNGR Advanced Material</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6165,12 +6145,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002</t>
+          <t>CASE_008; WB_001</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+          <t>中国基金报; 世界银行（World Bank）</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6192,7 +6172,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6202,12 +6182,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>DOC_001; CASE_002; CASE_003; TRD_003</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>美国商务部; 美国商务部（经律所解读）; 联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6229,7 +6209,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6239,12 +6219,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; SNE_001; ALB_001</t>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_004</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; SNE Research; 雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6266,7 +6246,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6276,12 +6256,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+          <t>TRD_003; SNE_001; WTO_001</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; SNE Research; 世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6303,27 +6283,27 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>EU_001; IRS_001; WH_002</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -6340,34 +6320,34 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; CASE_008; DHS_001; CASE_007</t>
+          <t>EU_001; IRS_001; WH_002</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>SNE Research; 中国基金报; 美国国土安全部（DHS，Federal Register）; C114通信网</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>案例标注为 Optional，不计入 missing / false positive</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_002</t>
+          <t>PLUS1_001</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -6377,27 +6357,27 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002</t>
+          <t>SNE_001; CASE_008; DHS_001</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+          <t>SNE Research; 中国基金报; 美国国土安全部（DHS，Federal Register）</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注为 Optional，不计入 missing / false positive</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6394,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -6424,12 +6404,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>WTO_004; WEF_001</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）; 世界经济论坛（WEF）</t>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6451,7 +6431,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -6461,12 +6441,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; SNE_001; WTO_001</t>
+          <t>MOFCOM_005; MOFCOM_003</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; SNE Research; 世界贸易组织（WTO）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6488,7 +6468,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -6498,12 +6478,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; BIS_002; XPEV_001</t>
+          <t>TRD_003; SNE_001; WTO_001</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 美国商务部工业与安全局（BIS）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; SNE Research; 世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6525,27 +6505,27 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WTO_004; IRS_001</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; BIS_002; XPEV_001</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国财政部/国税局（Federal Register）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -6562,64 +6542,64 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>SNE_001; WB_001; CASE_008</t>
+          <t>EU_001; WTO_004; IRS_001</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>SNE Research; 世界银行（World Bank）; 中国基金报</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>案例标注为 Optional，不计入 missing / false positive</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_003</t>
+          <t>PLUS1_002</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>比亚迪 BYD</t>
+          <t>宁德时代 CATL</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
+          <t>SNE_001; WB_001; CASE_008</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）</t>
+          <t>SNE Research; 世界银行（World Bank）; 中国基金报</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注为 Optional，不计入 missing / false positive</t>
         </is>
       </c>
     </row>
@@ -6636,27 +6616,27 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>WTO_004</t>
+          <t>DOC_001; CASE_002; CASE_003; WH_002; CASE_010</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>世界贸易组织（WTO）</t>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6653,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -6683,17 +6663,17 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; SNE_001; ALB_001</t>
+          <t>MOFCOM_005</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; SNE Research; 雅保公司（Albemarle Corporation，SEC EDGAR）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6690,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -6720,17 +6700,17 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+          <t>TRD_003; SNE_001; ALB_001</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; SNE Research; 雅保公司（Albemarle Corporation，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -6747,27 +6727,27 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WTO_004; WH_002; IRS_001</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6764,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -6794,12 +6774,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>WB_001; SNE_001</t>
+          <t>EU_001; WTO_004; WH_002; IRS_001</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）; SNE Research</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 世界贸易组织（WTO）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -6811,17 +6791,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_004</t>
+          <t>PLUS1_003</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>晶科能源 JinkoSolar</t>
+          <t>比亚迪 BYD</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -6831,12 +6811,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
+          <t>SNE_001; CASE_008; WB_001</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+          <t>SNE Research; 中国基金报; 世界银行（World Bank）</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -6858,27 +6838,27 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6875,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -6905,12 +6885,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_002; ITA_001</t>
+          <t>MOFCOM_004; MOFCOM_005</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 美国国际贸易管理局（ITA）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -6932,27 +6912,27 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_010; EU_001</t>
+          <t>TRD_003</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）; 美国白宫（经律所解读）; 欧洲议会与欧盟理事会（EUR-Lex / Official Journal）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -6969,44 +6949,44 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>WB_001</t>
+          <t>NIO_001; MOFCOM_002; ITA_001; BIS_002; MOFCOM_001</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 美国国际贸易管理局（ITA）; 美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>案例标注为 Optional，不计入 missing / false positive</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_005</t>
+          <t>PLUS1_004</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics</t>
+          <t>晶科能源 JinkoSolar</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -7016,12 +6996,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; CASE_003; DOC_001; CASE_010; TRD_003</t>
+          <t>EU_001; IRS_001; WH_002</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -7033,37 +7013,37 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>PLUS1_005</t>
+          <t>PLUS1_004</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>三星电子 Samsung Electronics</t>
+          <t>晶科能源 JinkoSolar</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>WB_001</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>世界银行（World Bank）</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注为 Optional，不计入 missing / false positive</t>
         </is>
       </c>
     </row>
@@ -7080,7 +7060,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -7090,12 +7070,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; WTO_001</t>
+          <t>CASE_002; DOC_001; CASE_003; TRD_003; WH_002</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
+          <t>美国商务部（经律所解读）; 美国商务部; 联合国商品贸易统计数据库（UN Comtrade）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -7117,27 +7097,27 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_004</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -7154,27 +7134,27 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WH_002; IRS_001</t>
+          <t>TRD_003; WTO_001</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -7191,81 +7171,81 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>WB_001; CASE_008</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）; 中国基金报</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>PLUS1_005</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+          <t>三星电子 Samsung Electronics</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
+          <t>EU_001; IRS_001; WH_002</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RETURN_001</t>
+          <t>PLUS1_005</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
+          <t>三星电子 Samsung Electronics</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -7275,12 +7255,12 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>TRD_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -7302,27 +7282,27 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+          <t>CASE_003; CASE_002; DOC_001; CASE_010; WH_002</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7319,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -7349,17 +7329,17 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WH_002; CASE_003; CASE_010</t>
+          <t>MOFCOM_005; MOFCOM_004</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国商务部（经律所解读）; 美国白宫（经律所解读）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Political Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7356,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -7386,12 +7366,12 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>CASE_007; WB_001</t>
+          <t>TRD_003; WTO_001</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>C114通信网; 世界银行（World Bank）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -7403,17 +7383,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>RETURN_001</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -7423,91 +7403,91 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>CASE_002; DOC_001; CASE_003; TRD_003; WTO_003</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）; 美国商务部; 联合国商品贸易统计数据库（UN Comtrade）; 世界贸易组织（WTO）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Trade Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>RETURN_001</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; ALB_001; WTO_001</t>
+          <t>EU_001; WH_002</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>RETURN_002</t>
+          <t>RETURN_001</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
+          <t>恩捷股份 Yunnan Energy New Material (Semcorp)</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+          <t>CASE_007</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+          <t>C114通信网</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7504,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -7534,17 +7514,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>EU_001; IRS_001; WH_002</t>
+          <t>CASE_002; DOC_001; CASE_003; USMCA_001</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
+          <t>美国商务部（经律所解读）; 美国商务部; 美国贸易代表办公室（USTR）</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Trade Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7541,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -7571,12 +7551,12 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>WB_001; CASE_008; CASE_001</t>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_004; MOFCOM_006</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）; 中国基金报; 路透社（Reuters）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻泰国大使馆经济商务处</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -7588,91 +7568,91 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>CASE_003; CASE_002; WH_002; CASE_010; TRD_003</t>
+          <t>TRD_003; ALB_001; WTO_001</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>美国商务部（经律所解读）; 美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）; 联合国商品贸易统计数据库（UN Comtrade）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Trade Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; CASE_001</t>
+          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -7682,54 +7662,54 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; BIS_002; MOFCOM_001; MOFCOM_002; XPEV_001</t>
+          <t>IRS_001; EU_001; WH_002</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 美国商务部工业与安全局（BIS）; 商务部、海关总署; 商务部</t>
+          <t>美国财政部/国税局（Federal Register）; 欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>RETURN_003</t>
+          <t>RETURN_002</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>制造业外迁企业（行业层面）</t>
+          <t>富士康 Foxconn / 苹果 Apple（供应链）</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>WH_002; CASE_010; EU_003</t>
+          <t>CASE_008</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）; 欧盟委员会（EUR-Lex / Official Journal）</t>
+          <t>中国基金报</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -7746,44 +7726,44 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk</t>
+          <t>Trade Risk</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>WB_001; CASE_001; DHS_001</t>
+          <t>CASE_002; CASE_003; CASE_010; WH_002; TRD_003</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>世界银行（World Bank）; 路透社（Reuters）; 美国国土安全部（DHS，Federal Register）</t>
+          <t>美国商务部（经律所解读）; 美国白宫（经律所解读）; 美国白宫贸易与制造业政策办公室; 联合国商品贸易统计数据库（UN Comtrade）</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>与案例标注一致</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Trade Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+          <t>制造业外迁企业（行业层面）</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk</t>
+          <t>Political Risk</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -7793,12 +7773,12 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>DOC_001; CASE_002; CASE_003; CASE_010</t>
+          <t>MOFCOM_004</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫（经律所解读）</t>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -7810,17 +7790,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+          <t>制造业外迁企业（行业层面）</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Political Risk</t>
+          <t>Supply Chain Risk</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -7830,12 +7810,12 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>WEF_001</t>
+          <t>TRD_003; CASE_001</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>世界经济论坛（WEF）</t>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 路透社（Reuters）</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -7847,17 +7827,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+          <t>制造业外迁企业（行业层面）</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Supply Chain Risk</t>
+          <t>Regulatory Risk</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -7867,34 +7847,34 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>TRD_003; ALB_001; WTO_001</t>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; BIS_002; XPEV_001</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 美国商务部工业与安全局（BIS）</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+          <t>制造业外迁企业（行业层面）</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Regulatory Risk</t>
+          <t>Market Access Risk</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -7904,54 +7884,54 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>NIO_001; MOFCOM_001; MOFCOM_002; XPEV_001; BIS_002</t>
+          <t>WH_002; CASE_010</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部、海关总署; 商务部; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+          <t>美国白宫贸易与制造业政策办公室; 美国白宫（经律所解读）</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RETURN_004</t>
+          <t>RETURN_003</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+          <t>制造业外迁企业（行业层面）</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Market Access Risk</t>
+          <t>Operational Risk</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>EU_001; WH_002; IRS_001</t>
+          <t>WB_001; CASE_001</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国白宫贸易与制造业政策办公室; 美国财政部/国税局（Federal Register）</t>
+          <t>世界银行（World Bank）; 路透社（Reuters）</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+          <t>与案例标注一致</t>
         </is>
       </c>
     </row>
@@ -7968,32 +7948,217 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>Trade Risk</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>DOC_001; CASE_002; CASE_003; CASE_010</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>美国商务部; 美国商务部（经律所解读）; 美国白宫（经律所解读）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Political Risk</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>MOFCOM_005; MOFCOM_003; MOFCOM_004</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻印度大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻越南大使馆经济商务处; 商务部对外投资和经济合作司、商务部国际贸易经济合作研究院、中国驻马来西亚大使馆经济商务处</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>与案例标注一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>TRD_003; ALB_001; WTO_001</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>联合国商品贸易统计数据库（UN Comtrade）; 雅保公司（Albemarle Corporation，SEC EDGAR）; 世界贸易组织（WTO）</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Supply Chain Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Risk</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>NIO_001; MOFCOM_002; MOFCOM_001; XPEV_001; BIS_002</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>蔚来（NIO Inc.，SEC EDGAR）; 商务部; 商务部、海关总署; 小鹏汽车（XPeng Inc.，SEC EDGAR）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Regulatory Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Market Access Risk</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>EU_001; IRS_001; WH_002</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>欧洲议会与欧盟理事会（EUR-Lex / Official Journal）; 美国财政部/国税局（Federal Register）; 美国白宫贸易与制造业政策办公室</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>案例标注未列该类，但证据带 Task 1 related_risk=Market Access Risk 标签，属「标注口径」差异，可复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>RETURN_004</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>蜂巢能源 SVOLT（欧洲业务）</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
           <t>Operational Risk</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>TSLA_001; CASE_008; WB_001</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）; 中国基金报; 世界银行（World Bank）</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>TSLA_001; CASE_008</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>特斯拉公司（Tesla, Inc.，SEC EDGAR）; 中国基金报</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>与案例标注一致</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G98"/>
+  <autoFilter ref="A1:G103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8265,7 +8430,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8705,7 +8870,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8730,7 +8895,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="K13" s="2" t="n">
@@ -8815,7 +8980,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -8870,7 +9035,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8895,7 +9060,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K16" s="2" t="n">
@@ -8925,7 +9090,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8950,7 +9115,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="K17" s="2" t="n">
@@ -9067,13 +9232,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.799</v>
+        <v>0.887</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.681</v>
+        <v>0.701</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.946</v>
+        <v>1</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -9088,13 +9253,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.61</v>
+        <v>0.598</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.535</v>
+        <v>0.539</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -9109,13 +9274,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -9130,13 +9295,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -9161,7 +9326,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L1：语料层面。六类风险在 49 篇语料中均有标注（不含 held-out 案例），缺失的是「与案例挂钩」的证据</t>
+          <t>L1：语料层面。六类风险在 53 篇语料中均有标注（不含 held-out 案例），缺失的是「与案例挂钩」的证据</t>
         </is>
       </c>
     </row>
@@ -9172,13 +9337,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.946</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.946</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.946</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -9193,13 +9358,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.799</v>
+        <v>0.887</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.681</v>
+        <v>0.701</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.946</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -9225,7 +9390,7 @@
       <c r="D10" s="2" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Trade Risk=20; Political Risk=9; Supply Chain Risk=21; Regulatory Risk=15; Market Access Risk=24; Operational Risk=13</t>
+          <t>Trade Risk=20; Political Risk=13; Supply Chain Risk=21; Regulatory Risk=19; Market Access Risk=24; Operational Risk=13</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9427,7 @@
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Operational Risk 记为 Optional，不计入 missing / false positive；本评测测的是证据链能否支撑风险识别，不是 LLM 生成风险的质量。risk_dimension 的 Precision 低于基线主要是口径效应：39 次误报里 Regulatory 14 次、Market Access 11 次，均可追溯到中国侧出口管制 / 公司披露与欧盟法规证据；逐条归因见 FP Attribution sheet</t>
+          <t>Operational Risk 记为 Optional，不计入 missing / false positive；本评测测的是证据链能否支撑风险识别，不是 LLM 生成风险的质量。risk_dimension 的 Precision 低于基线主要是口径效应：41 次误报里 Regulatory 14 次、Market Access 11 次，均可追溯到中国侧出口管制 / 公司披露与欧盟法规证据；逐条归因见 FP Attribution sheet</t>
         </is>
       </c>
     </row>
